--- a/zapata_Asientos/asientos.xlsx
+++ b/zapata_Asientos/asientos.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Desarrollo\Python\CalculoPilotes\zapata_Asientos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A75AE4-29BA-4897-B579-B382051F3290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AA95FF-E51F-4876-90F4-15A58E6FCF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>B=</t>
   </si>
@@ -75,18 +75,96 @@
   </si>
   <si>
     <t>nu</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+        <charset val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>si+1</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>i+1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Symbol"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <charset val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -110,12 +188,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -447,10 +537,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="A3:I22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -461,18 +555,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -483,14 +577,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:6">
+      <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -507,76 +601,180 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="1">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="C9" s="1">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="D9" s="1">
         <f>C9-B9</f>
-        <v>15</v>
+        <v>1.4990000000000001</v>
       </c>
       <c r="E9">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="1">
         <f>C9</f>
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="C10" s="1">
-        <v>25</v>
+        <f>+B10+3</f>
+        <v>4.5</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" ref="D10:D11" si="0">C10-B10</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="F10" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1">
         <f>C10</f>
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="C11" s="1">
-        <v>30</v>
+        <f>B11+5</f>
+        <v>9.5</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="E11">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="F11" s="1">
         <v>0.25</v>
       </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1">
+        <f>$B$4/$B$3</f>
+        <v>1</v>
+      </c>
+      <c r="B19" s="3">
+        <f>2*B9/$B$3</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C19" s="3">
+        <f>2*C9/$B$3</f>
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="6">
+        <f>(LN((SQRT(1+$A$19^2+B19^2)+$A$19)/(SQRT(1+$A$19^2+B19^2)-$A$19))+$A$19*LN((SQRT(1+$A$19^2+B19^2)+1)/(SQRT(1+$A$19^2+B19^2))-1))</f>
+        <v>1.4161726266528365</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1">
+        <f t="shared" ref="A20:A21" si="1">$B$4/$B$3</f>
+        <v>1</v>
+      </c>
+      <c r="B20" s="3">
+        <f t="shared" ref="B20:C20" si="2">2*B10/$B$3</f>
+        <v>1.5</v>
+      </c>
+      <c r="C20" s="3">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+      <c r="D20" s="6">
+        <f t="shared" ref="D20:D21" si="3">(LN((SQRT(1+$A$19^2+B20^2)+$A$19)/(SQRT(1+$A$19^2+B20^2)-$A$19))+$A$19*LN((SQRT(1+$A$19^2+B20^2)+1)/(SQRT(1+$A$19^2+B20^2))-1))</f>
+        <v>0.33572999702767647</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B21" s="3">
+        <f t="shared" ref="B21:C21" si="4">2*B11/$B$3</f>
+        <v>4.5</v>
+      </c>
+      <c r="C21" s="3">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="D21" s="6">
+        <f>(LN((SQRT(1+$A$19^2+B21^2)+$A$19)/(SQRT(1+$A$19^2+B21^2)-$A$19))+$A$19*LN((SQRT(1+$A$19^2+B21^2)+1)/(SQRT(1+$A$19^2+B21^2))-1))</f>
+        <v>-1.1206428154380457</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>